--- a/tests/fixtures/import-ux/检测记录.xlsx
+++ b/tests/fixtures/import-ux/检测记录.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1-WW-FR-008-0003-000</t>
+          <t>1G-SLB-WB-F000-R003-Q001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,14 +497,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>前墙第8排第3管</t>
+          <t>前墙第3根</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1-WW-FR-008-0004-000</t>
+          <t>1G-SLB-WB-F000-R004-Q001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,7 +546,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1-WW-FR-008-0004-000</t>
+          <t>1G-SLB-WB-F000-R004-Q001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1-WW-FR-021-0011-000</t>
+          <t>1G-SLB-WB-B000-R011-Q001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
